--- a/workshop_prep/sales_bridge_waterfall.xlsx
+++ b/workshop_prep/sales_bridge_waterfall.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1 - Total Company" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1a - Special Accounts vs Core" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2 - Core Composition" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3 - Continuing Grow-Decline" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4 - By Layer (Continuing LFL)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4b - Franchise Detail w Layer" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 - Total Company" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1a - Special Accounts vs Core" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 - Core Composition" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 - Continuing Grow-Decline" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 - By Layer (Continuing LFL)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4b - Franchise Detail w Layer" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD2026 Special Accounts" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24338,4 +24339,139 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>FY2025_Full_Year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>YTD2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XXL SE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>81913672</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-6885</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>XXL NO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>33735862</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-6906</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ZALANDO</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>52597798</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20854009</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>49134024</v>
+      </c>
+      <c r="C5" t="n">
+        <v>17087984</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STADIUM Outlet</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9555693</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7595412</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ZALANDO MARKETPLACE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>456250</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALL SPECIAL ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>227393297</v>
+      </c>
+      <c r="C8" t="n">
+        <v>45523614</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Special % of total sales</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>